--- a/dados_teste/Indicadores_Poda.xlsx
+++ b/dados_teste/Indicadores_Poda.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-24375" yWindow="1680" windowWidth="21600" windowHeight="11235" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planilha1" sheetId="1" state="visible" r:id="rId1"/>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="32.44140625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C128" t="n">
         <v>25310</v>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C129" t="n">
         <v>4266</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C130" t="n">
         <v>469989</v>
@@ -3086,7 +3086,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C131" t="n">
         <v>1943977</v>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C132" t="n">
         <v>10051272</v>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C133" t="n">
         <v>1951</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C134" t="n">
         <v>617168</v>
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C135" t="n">
         <v>564968</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C136" t="n">
         <v>68541</v>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C137" t="n">
-        <v>107474</v>
+        <v>107898</v>
       </c>
       <c r="D137" t="n">
-        <v>2395931</v>
+        <v>2397657</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C138" t="n">
         <v>58</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C139" t="n">
         <v>33054</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C140" t="n">
         <v>83288</v>
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C141" t="n">
         <v>109958</v>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C142" t="n">
         <v>21186816</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C143" t="n">
         <v>966</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C144" t="n">
         <v>15750</v>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C145" t="n">
         <v>55251</v>
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C146" t="n">
         <v>60576</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C147" t="n">
         <v>84380</v>
@@ -3405,419 +3405,20 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Alho verde</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C148" t="n">
-        <v>12885</v>
+        <v>96565249</v>
       </c>
       <c r="D148" t="n">
-        <v>172832</v>
+        <v>1154220084</v>
       </c>
       <c r="E148" t="n">
-        <v>21733.72</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Abacates</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C149" t="n">
-        <v>25310</v>
-      </c>
-      <c r="D149" t="n">
-        <v>427457</v>
-      </c>
-      <c r="E149" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Alho verde</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C150" t="n">
-        <v>12885</v>
-      </c>
-      <c r="D150" t="n">
-        <v>172832</v>
-      </c>
-      <c r="E150" t="n">
-        <v>21733.72</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Azeitonas</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C151" t="n">
-        <v>4266</v>
-      </c>
-      <c r="D151" t="n">
-        <v>4499</v>
-      </c>
-      <c r="E151" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Banana</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C152" t="n">
-        <v>469989</v>
-      </c>
-      <c r="D152" t="n">
-        <v>7046345</v>
-      </c>
-      <c r="E152" t="n">
-        <v>2472.18</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Café, verde</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C153" t="n">
-        <v>1943977</v>
-      </c>
-      <c r="D153" t="n">
-        <v>3387724</v>
-      </c>
-      <c r="E153" t="n">
-        <v>11573.57</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Cana-de-Açúcar</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C154" t="n">
-        <v>10051272</v>
-      </c>
-      <c r="D154" t="n">
-        <v>759662482</v>
-      </c>
-      <c r="E154" t="n">
-        <v>692.89</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Figos</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C155" t="n">
-        <v>1951</v>
-      </c>
-      <c r="D155" t="n">
-        <v>20586</v>
-      </c>
-      <c r="E155" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Grãos de cacau</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C156" t="n">
-        <v>617168</v>
-      </c>
-      <c r="D156" t="n">
-        <v>297509</v>
-      </c>
-      <c r="E156" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Laranjas</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C157" t="n">
-        <v>564968</v>
-      </c>
-      <c r="D157" t="n">
-        <v>15688409</v>
-      </c>
-      <c r="E157" t="n">
-        <v>3988.99</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Limões e limas</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C158" t="n">
-        <v>68541</v>
-      </c>
-      <c r="D158" t="n">
-        <v>1722845</v>
-      </c>
-      <c r="E158" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Mangas, goiabas e mangostões</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C159" t="n">
-        <v>107474</v>
-      </c>
-      <c r="D159" t="n">
-        <v>2395931</v>
-      </c>
-      <c r="E159" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Marmelos</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C160" t="n">
-        <v>58</v>
-      </c>
-      <c r="D160" t="n">
-        <v>411</v>
-      </c>
-      <c r="E160" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Maçãs</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C161" t="n">
-        <v>33054</v>
-      </c>
-      <c r="D161" t="n">
-        <v>997470</v>
-      </c>
-      <c r="E161" t="n">
-        <v>6188</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Melancias</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C162" t="n">
-        <v>83288</v>
-      </c>
-      <c r="D162" t="n">
-        <v>1978702</v>
-      </c>
-      <c r="E162" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Melões e outros melões</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C163" t="n">
-        <v>31287</v>
-      </c>
-      <c r="D163" t="n">
-        <v>816939</v>
-      </c>
-      <c r="E163" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Milho</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C164" t="n">
-        <v>21186816</v>
-      </c>
-      <c r="D164" t="n">
-        <v>115302207</v>
-      </c>
-      <c r="E164" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Peras</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C165" t="n">
-        <v>966</v>
-      </c>
-      <c r="D165" t="n">
-        <v>14473</v>
-      </c>
-      <c r="E165" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Pêssegos e nectarinas</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C166" t="n">
-        <v>15750</v>
-      </c>
-      <c r="D166" t="n">
-        <v>194639</v>
-      </c>
-      <c r="E166" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Tangerinas, tangerinas, clementinas</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C167" t="n">
-        <v>55251</v>
-      </c>
-      <c r="D167" t="n">
-        <v>1016575</v>
-      </c>
-      <c r="E167" t="n">
-        <v>2237.87</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Tomates</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C168" t="n">
-        <v>60576</v>
-      </c>
-      <c r="D168" t="n">
-        <v>4407502</v>
-      </c>
-      <c r="E168" t="n">
-        <v>17738.36</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Uvas</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C169" t="n">
-        <v>84380</v>
-      </c>
-      <c r="D169" t="n">
-        <v>1820104</v>
-      </c>
-      <c r="E169" t="n">
-        <v>0</v>
+        <v>122747.99</v>
       </c>
     </row>
   </sheetData>
